--- a/ig/nr-add-sato2-profile/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/nr-add-sato2-profile/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3533" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3533" uniqueCount="647">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-17T15:33:27+00:00</t>
+    <t>2023-11-17T15:40:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -441,6 +441,9 @@
   </si>
   <si>
     <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’une oid : « urn:oid:xx.xx.xx »</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -3399,10 +3402,10 @@
         <v>136</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3452,7 +3455,7 @@
         <v>80</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -3487,10 +3490,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -3513,16 +3516,16 @@
         <v>92</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -3572,7 +3575,7 @@
         <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -3607,10 +3610,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3633,16 +3636,16 @@
         <v>92</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3668,13 +3671,13 @@
         <v>80</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>80</v>
@@ -3692,7 +3695,7 @@
         <v>80</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3713,10 +3716,10 @@
         <v>80</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>80</v>
@@ -3727,10 +3730,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3753,16 +3756,16 @@
         <v>92</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3788,13 +3791,13 @@
         <v>80</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>80</v>
@@ -3812,7 +3815,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3833,10 +3836,10 @@
         <v>80</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>80</v>
@@ -3847,10 +3850,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3876,13 +3879,13 @@
         <v>135</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3932,7 +3935,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3967,10 +3970,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3993,16 +3996,16 @@
         <v>80</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4028,13 +4031,13 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -4052,7 +4055,7 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -4087,14 +4090,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -4113,16 +4116,16 @@
         <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4172,7 +4175,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -4196,7 +4199,7 @@
         <v>80</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>80</v>
@@ -4207,14 +4210,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4233,16 +4236,16 @@
         <v>80</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4292,7 +4295,7 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -4327,10 +4330,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4359,7 +4362,7 @@
         <v>115</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N17" t="s" s="2">
         <v>117</v>
@@ -4412,7 +4415,7 @@
         <v>120</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -4447,13 +4450,13 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>80</v>
@@ -4475,13 +4478,13 @@
         <v>80</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4532,7 +4535,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4567,13 +4570,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>80</v>
@@ -4595,13 +4598,13 @@
         <v>80</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4652,7 +4655,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4687,10 +4690,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4716,16 +4719,16 @@
         <v>114</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>80</v>
@@ -4774,7 +4777,7 @@
         <v>120</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4809,10 +4812,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4835,17 +4838,17 @@
         <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>80</v>
@@ -4894,7 +4897,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4909,19 +4912,19 @@
         <v>104</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>80</v>
@@ -4929,14 +4932,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4955,19 +4958,19 @@
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -5016,7 +5019,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -5028,19 +5031,19 @@
         <v>103</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>80</v>
@@ -5051,14 +5054,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5077,16 +5080,16 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5136,7 +5139,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -5148,19 +5151,19 @@
         <v>103</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>80</v>
@@ -5171,10 +5174,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5197,19 +5200,19 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -5234,13 +5237,13 @@
         <v>80</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>80</v>
@@ -5258,7 +5261,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>91</v>
@@ -5273,19 +5276,19 @@
         <v>104</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>80</v>
@@ -5293,10 +5296,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5319,19 +5322,19 @@
         <v>80</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -5356,19 +5359,19 @@
         <v>80</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
@@ -5378,7 +5381,7 @@
         <v>120</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -5399,13 +5402,13 @@
         <v>80</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>80</v>
@@ -5413,13 +5416,13 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>80</v>
@@ -5441,19 +5444,19 @@
         <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>80</v>
@@ -5478,13 +5481,13 @@
         <v>80</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>80</v>
@@ -5502,7 +5505,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5523,13 +5526,13 @@
         <v>80</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>80</v>
@@ -5537,10 +5540,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5655,10 +5658,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5775,10 +5778,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5801,19 +5804,19 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>80</v>
@@ -5862,7 +5865,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5883,10 +5886,10 @@
         <v>80</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>80</v>
@@ -5897,10 +5900,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6015,10 +6018,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6135,10 +6138,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6164,23 +6167,23 @@
         <v>135</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>80</v>
@@ -6222,7 +6225,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -6243,10 +6246,10 @@
         <v>80</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>80</v>
@@ -6257,10 +6260,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6286,13 +6289,13 @@
         <v>107</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6342,7 +6345,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6363,10 +6366,10 @@
         <v>80</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>80</v>
@@ -6377,10 +6380,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6403,26 +6406,26 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>80</v>
@@ -6464,7 +6467,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6485,10 +6488,10 @@
         <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>80</v>
@@ -6499,10 +6502,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6528,16 +6531,16 @@
         <v>107</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>80</v>
@@ -6586,7 +6589,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6607,10 +6610,10 @@
         <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>80</v>
@@ -6621,10 +6624,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6647,19 +6650,19 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
@@ -6708,7 +6711,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6729,10 +6732,10 @@
         <v>80</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>80</v>
@@ -6743,10 +6746,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6772,16 +6775,16 @@
         <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -6830,7 +6833,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6851,10 +6854,10 @@
         <v>80</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>80</v>
@@ -6865,14 +6868,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6891,19 +6894,19 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -6913,7 +6916,7 @@
         <v>80</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>80</v>
@@ -6928,13 +6931,13 @@
         <v>80</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>80</v>
@@ -6952,7 +6955,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>91</v>
@@ -6967,30 +6970,30 @@
         <v>104</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7013,19 +7016,19 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
@@ -7074,7 +7077,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -7086,22 +7089,22 @@
         <v>103</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>80</v>
@@ -7109,10 +7112,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7135,16 +7138,16 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7194,7 +7197,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -7206,7 +7209,7 @@
         <v>103</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>80</v>
@@ -7215,13 +7218,13 @@
         <v>80</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>80</v>
@@ -7229,14 +7232,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7255,19 +7258,19 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -7316,7 +7319,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7328,22 +7331,22 @@
         <v>103</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>80</v>
@@ -7351,14 +7354,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7377,19 +7380,19 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>80</v>
@@ -7438,7 +7441,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7447,25 +7450,25 @@
         <v>91</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>80</v>
@@ -7473,10 +7476,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7502,13 +7505,13 @@
         <v>129</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7558,7 +7561,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7579,13 +7582,13 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>80</v>
@@ -7593,10 +7596,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7619,19 +7622,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>80</v>
@@ -7680,7 +7683,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7692,22 +7695,22 @@
         <v>103</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>80</v>
@@ -7715,10 +7718,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7741,19 +7744,19 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>80</v>
@@ -7763,7 +7766,7 @@
         <v>80</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>80</v>
@@ -7802,7 +7805,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7811,7 +7814,7 @@
         <v>91</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>104</v>
@@ -7820,27 +7823,27 @@
         <v>80</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7955,10 +7958,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8075,10 +8078,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8101,19 +8104,19 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -8162,7 +8165,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -8183,10 +8186,10 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>80</v>
@@ -8197,10 +8200,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8223,25 +8226,25 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q49" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R49" t="s" s="2">
         <v>80</v>
@@ -8262,13 +8265,13 @@
         <v>80</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>80</v>
@@ -8286,7 +8289,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -8307,10 +8310,10 @@
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>80</v>
@@ -8321,10 +8324,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8350,16 +8353,16 @@
         <v>107</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8408,7 +8411,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8429,10 +8432,10 @@
         <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>80</v>
@@ -8443,10 +8446,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8472,16 +8475,16 @@
         <v>135</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -8530,7 +8533,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8539,7 +8542,7 @@
         <v>91</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>104</v>
@@ -8551,10 +8554,10 @@
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>80</v>
@@ -8565,10 +8568,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8591,19 +8594,19 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8652,7 +8655,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8673,10 +8676,10 @@
         <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>80</v>
@@ -8687,10 +8690,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8713,19 +8716,19 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -8750,13 +8753,13 @@
         <v>80</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
@@ -8774,7 +8777,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8783,7 +8786,7 @@
         <v>91</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>104</v>
@@ -8798,7 +8801,7 @@
         <v>105</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>80</v>
@@ -8809,10 +8812,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8927,10 +8930,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9047,10 +9050,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9073,19 +9076,19 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>80</v>
@@ -9134,7 +9137,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -9155,10 +9158,10 @@
         <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>80</v>
@@ -9169,10 +9172,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9287,10 +9290,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9407,10 +9410,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9436,16 +9439,16 @@
         <v>135</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
@@ -9494,7 +9497,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9515,10 +9518,10 @@
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>80</v>
@@ -9529,10 +9532,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9558,13 +9561,13 @@
         <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9614,7 +9617,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9635,10 +9638,10 @@
         <v>80</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>80</v>
@@ -9649,10 +9652,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9675,19 +9678,19 @@
         <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>80</v>
@@ -9736,7 +9739,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9757,10 +9760,10 @@
         <v>80</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>80</v>
@@ -9771,10 +9774,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9800,16 +9803,16 @@
         <v>107</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>80</v>
@@ -9858,7 +9861,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9879,10 +9882,10 @@
         <v>80</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>80</v>
@@ -9893,10 +9896,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9919,19 +9922,19 @@
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>80</v>
@@ -9980,7 +9983,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -10001,10 +10004,10 @@
         <v>80</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>80</v>
@@ -10015,10 +10018,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10044,16 +10047,16 @@
         <v>107</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>80</v>
@@ -10102,7 +10105,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -10123,10 +10126,10 @@
         <v>80</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>80</v>
@@ -10137,14 +10140,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -10163,19 +10166,19 @@
         <v>80</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
@@ -10200,13 +10203,13 @@
         <v>80</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>80</v>
@@ -10224,7 +10227,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -10242,27 +10245,27 @@
         <v>80</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10285,19 +10288,19 @@
         <v>80</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>80</v>
@@ -10346,7 +10349,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -10367,10 +10370,10 @@
         <v>80</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>80</v>
@@ -10381,10 +10384,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10407,16 +10410,16 @@
         <v>80</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10442,13 +10445,13 @@
         <v>80</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>80</v>
@@ -10466,7 +10469,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10484,27 +10487,27 @@
         <v>80</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10527,19 +10530,19 @@
         <v>80</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -10564,13 +10567,13 @@
         <v>80</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>80</v>
@@ -10588,7 +10591,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10609,10 +10612,10 @@
         <v>80</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>80</v>
@@ -10623,10 +10626,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10649,16 +10652,16 @@
         <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10708,7 +10711,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10720,33 +10723,33 @@
         <v>103</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10769,16 +10772,16 @@
         <v>80</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10828,7 +10831,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10840,33 +10843,33 @@
         <v>103</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10889,19 +10892,19 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>80</v>
@@ -10950,7 +10953,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10962,7 +10965,7 @@
         <v>103</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>80</v>
@@ -10971,10 +10974,10 @@
         <v>80</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>80</v>
@@ -10985,10 +10988,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11103,10 +11106,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11223,14 +11226,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11252,16 +11255,16 @@
         <v>114</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>80</v>
@@ -11310,7 +11313,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -11345,10 +11348,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11371,16 +11374,16 @@
         <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11430,7 +11433,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11439,10 +11442,10 @@
         <v>91</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>80</v>
@@ -11451,10 +11454,10 @@
         <v>80</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>80</v>
@@ -11465,10 +11468,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11491,16 +11494,16 @@
         <v>80</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11550,7 +11553,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11559,10 +11562,10 @@
         <v>91</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>80</v>
@@ -11571,10 +11574,10 @@
         <v>80</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>80</v>
@@ -11585,10 +11588,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11611,19 +11614,19 @@
         <v>80</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>80</v>
@@ -11648,13 +11651,13 @@
         <v>80</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>80</v>
@@ -11672,7 +11675,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11690,13 +11693,13 @@
         <v>80</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>80</v>
@@ -11707,10 +11710,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11733,19 +11736,19 @@
         <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>80</v>
@@ -11770,13 +11773,13 @@
         <v>80</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>80</v>
@@ -11794,7 +11797,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11812,13 +11815,13 @@
         <v>80</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>80</v>
@@ -11829,10 +11832,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11855,19 +11858,19 @@
         <v>80</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>80</v>
@@ -11916,7 +11919,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11928,7 +11931,7 @@
         <v>103</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>80</v>
@@ -11937,10 +11940,10 @@
         <v>80</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>80</v>
@@ -11951,10 +11954,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11980,13 +11983,13 @@
         <v>107</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -12036,7 +12039,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -12057,10 +12060,10 @@
         <v>80</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>80</v>
@@ -12071,10 +12074,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12097,16 +12100,16 @@
         <v>92</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12156,7 +12159,7 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -12168,7 +12171,7 @@
         <v>103</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>80</v>
@@ -12177,10 +12180,10 @@
         <v>80</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>80</v>
@@ -12191,10 +12194,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12217,16 +12220,16 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12276,7 +12279,7 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -12288,7 +12291,7 @@
         <v>103</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>80</v>
@@ -12297,10 +12300,10 @@
         <v>80</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>80</v>
@@ -12311,10 +12314,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12337,19 +12340,19 @@
         <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>80</v>
@@ -12398,7 +12401,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12410,7 +12413,7 @@
         <v>103</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>80</v>
@@ -12419,10 +12422,10 @@
         <v>80</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>80</v>
@@ -12433,10 +12436,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12551,10 +12554,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12671,14 +12674,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12700,16 +12703,16 @@
         <v>114</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N86" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>80</v>
@@ -12758,7 +12761,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12793,10 +12796,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12819,19 +12822,19 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>80</v>
@@ -12856,13 +12859,13 @@
         <v>80</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>80</v>
@@ -12880,7 +12883,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>91</v>
@@ -12898,16 +12901,16 @@
         <v>80</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>80</v>
@@ -12915,10 +12918,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12941,19 +12944,19 @@
         <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>80</v>
@@ -12978,13 +12981,13 @@
         <v>80</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>80</v>
@@ -13002,7 +13005,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -13011,7 +13014,7 @@
         <v>91</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>104</v>
@@ -13020,27 +13023,27 @@
         <v>80</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13063,19 +13066,19 @@
         <v>80</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>80</v>
@@ -13100,13 +13103,13 @@
         <v>80</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>80</v>
@@ -13124,7 +13127,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -13133,7 +13136,7 @@
         <v>91</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>104</v>
@@ -13148,7 +13151,7 @@
         <v>105</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>80</v>
@@ -13159,14 +13162,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -13185,19 +13188,19 @@
         <v>80</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>80</v>
@@ -13222,13 +13225,13 @@
         <v>80</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>80</v>
@@ -13246,7 +13249,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13264,27 +13267,27 @@
         <v>80</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13310,16 +13313,16 @@
         <v>81</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>80</v>
@@ -13368,7 +13371,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -13389,10 +13392,10 @@
         <v>80</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>80</v>

--- a/ig/nr-add-sato2-profile/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/ig/nr-add-sato2-profile/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-17T15:40:40+00:00</t>
+    <t>2023-11-23T10:07:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
